--- a/data/daschland_ontology/project-metadata (Project Metadata)/resources.xlsx
+++ b/data/daschland_ontology/project-metadata (Project Metadata)/resources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/daschland-scripts/daschland_ontology/project-metadata (Project Metadata)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noraammann/Documents/Cloned_GitHub/0854-daschland-scripts/data/daschland_ontology/project-metadata (Project Metadata)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE3A567-E162-8C40-8774-2530576C235A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DE7682-42C5-5B4A-90EC-02811F3709D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48680" yWindow="500" windowWidth="26260" windowHeight="24240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="classes" sheetId="1" r:id="rId1"/>
@@ -445,7 +445,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="53">
   <si>
     <t>name</t>
   </si>
@@ -544,18 +544,6 @@
   </si>
   <si>
     <t>hasFileSize</t>
-  </si>
-  <si>
-    <t>1-n</t>
-  </si>
-  <si>
-    <t>hasAuthorshipResource</t>
-  </si>
-  <si>
-    <t>hasCopyrightResource</t>
-  </si>
-  <si>
-    <t>hasLicenseResource</t>
   </si>
   <si>
     <t>default_permissions_overrule</t>
@@ -1098,16 +1086,16 @@
         <v>16</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>17</v>
@@ -1130,16 +1118,16 @@
         <v>22</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>23</v>
@@ -1147,34 +1135,34 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="G4" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="H4" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="15" t="s">
+      <c r="L4" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2172,7 +2160,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.33203125" customWidth="1"/>
@@ -2189,7 +2177,7 @@
         <v>26</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2216,7 +2204,7 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>30</v>
@@ -2245,39 +2233,6 @@
       </c>
       <c r="C6">
         <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="8">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2247,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48BB4D76-6E56-BC47-A642-3A8C7BCF9D1B}">
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.1640625" customWidth="1"/>
@@ -2381,7 +2336,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>30</v>
@@ -2461,15 +2416,9 @@
       <c r="S6" s="13"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="13">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13">
-        <v>6</v>
-      </c>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
@@ -2488,15 +2437,9 @@
       <c r="S7" s="13"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="13">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13">
-        <v>7</v>
-      </c>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
@@ -2515,15 +2458,9 @@
       <c r="S8" s="13"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="13">
-        <v>8</v>
-      </c>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
@@ -3549,69 +3486,6 @@
       <c r="R57" s="13"/>
       <c r="S57" s="13"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A58" s="13"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
-      <c r="L58" s="13"/>
-      <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="13"/>
-      <c r="P58" s="13"/>
-      <c r="Q58" s="13"/>
-      <c r="R58" s="13"/>
-      <c r="S58" s="13"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A59" s="13"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="13"/>
-      <c r="Q59" s="13"/>
-      <c r="R59" s="13"/>
-      <c r="S59" s="13"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A60" s="13"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="13"/>
-      <c r="Q60" s="13"/>
-      <c r="R60" s="13"/>
-      <c r="S60" s="13"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3619,7 +3493,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
@@ -3660,7 +3534,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>30</v>
@@ -3689,39 +3563,6 @@
       </c>
       <c r="C6">
         <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="8">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
